--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21544,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21698,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22083,7 +22083,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22391,7 +22391,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22622,7 +22622,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22699,7 +22699,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22776,7 +22776,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22930,7 +22930,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23238,7 +23238,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23315,7 +23315,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23392,7 +23392,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23546,7 +23546,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23781,7 +23781,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23939,7 +23939,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24018,7 +24018,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24097,7 +24097,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24176,7 +24176,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24255,7 +24255,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24413,7 +24413,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24492,7 +24492,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24650,7 +24650,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24729,7 +24729,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25045,7 +25045,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25124,7 +25124,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25519,7 +25519,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25598,7 +25598,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25677,7 +25677,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25756,7 +25756,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25835,7 +25835,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26072,7 +26072,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26151,7 +26151,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26230,7 +26230,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26309,7 +26309,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21544,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21698,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22083,7 +22083,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22391,7 +22391,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22622,7 +22622,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22699,7 +22699,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22776,7 +22776,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22930,7 +22930,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23238,7 +23238,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23315,7 +23315,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23392,7 +23392,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23546,7 +23546,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23781,7 +23781,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23939,7 +23939,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24018,7 +24018,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24097,7 +24097,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24176,7 +24176,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24255,7 +24255,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24413,7 +24413,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24492,7 +24492,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24650,7 +24650,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24729,7 +24729,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25045,7 +25045,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25124,7 +25124,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25519,7 +25519,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25598,7 +25598,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25677,7 +25677,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25756,7 +25756,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25835,7 +25835,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26072,7 +26072,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26151,7 +26151,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26230,7 +26230,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26309,7 +26309,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q336"/>
+  <dimension ref="A1:Q337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,10 +16159,14 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q205" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q205" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -16236,10 +16240,14 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q206" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q206" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -16313,10 +16321,14 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q207" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q207" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -16390,10 +16402,14 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q208" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q208" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -16467,10 +16483,14 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q209" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q209" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -16544,10 +16564,14 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q210" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q210" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -16621,10 +16645,14 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q211" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q211" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -16698,10 +16726,14 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q212" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q212" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -16775,10 +16807,14 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q213" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q213" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -16852,10 +16888,14 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q214" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q214" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -16929,10 +16969,14 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q215" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q215" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -17006,10 +17050,14 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q216" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q216" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -17083,10 +17131,14 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q217" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q217" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -17160,10 +17212,14 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q218" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q218" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -17237,10 +17293,14 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q219" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q219" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -17314,10 +17374,14 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q220" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q220" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -17391,10 +17455,14 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q221" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q221" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
@@ -17468,10 +17536,14 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q222" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q222" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -17545,10 +17617,14 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q223" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q223" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
@@ -17622,10 +17698,14 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q224" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q224" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -17699,10 +17779,14 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q225" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q225" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
@@ -17776,10 +17860,14 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q226" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q226" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
@@ -17853,10 +17941,14 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q227" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q227" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
@@ -17930,10 +18022,14 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q228" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q228" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
@@ -18007,10 +18103,14 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q229" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q229" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -18084,10 +18184,14 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q230" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q230" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
@@ -18161,10 +18265,14 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q231" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q231" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
@@ -18238,10 +18346,14 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q232" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q232" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
@@ -18315,10 +18427,14 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q233" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q233" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
@@ -18392,10 +18508,14 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q234" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q234" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -18461,9 +18581,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N235" s="6" t="n">
-        <v>48.56</v>
-      </c>
+      <c r="N235" s="4" t="n"/>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18471,10 +18589,14 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q235" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q235" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
@@ -18540,9 +18662,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N236" s="6" t="n">
-        <v>49.027</v>
-      </c>
+      <c r="N236" s="4" t="n"/>
       <c r="O236" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18550,10 +18670,14 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q236" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q236" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
@@ -18619,9 +18743,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N237" s="6" t="n">
-        <v>49.439</v>
-      </c>
+      <c r="N237" s="4" t="n"/>
       <c r="O237" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18629,10 +18751,14 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q237" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q237" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
@@ -18698,9 +18824,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N238" s="6" t="n">
-        <v>49.121</v>
-      </c>
+      <c r="N238" s="4" t="n"/>
       <c r="O238" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18708,10 +18832,14 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q238" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q238" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -18777,9 +18905,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N239" s="6" t="n">
-        <v>48.519</v>
-      </c>
+      <c r="N239" s="4" t="n"/>
       <c r="O239" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18787,10 +18913,14 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q239" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q239" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
@@ -18856,9 +18986,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N240" s="6" t="n">
-        <v>48.502</v>
-      </c>
+      <c r="N240" s="4" t="n"/>
       <c r="O240" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18866,10 +18994,14 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q240" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q240" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -18935,9 +19067,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N241" s="6" t="n">
-        <v>48.683</v>
-      </c>
+      <c r="N241" s="4" t="n"/>
       <c r="O241" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18945,10 +19075,14 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q241" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q241" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
@@ -19014,9 +19148,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N242" s="6" t="n">
-        <v>48.743</v>
-      </c>
+      <c r="N242" s="4" t="n"/>
       <c r="O242" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19024,10 +19156,14 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q242" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q242" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
@@ -19093,9 +19229,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N243" s="6" t="n">
-        <v>48.976</v>
-      </c>
+      <c r="N243" s="4" t="n"/>
       <c r="O243" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19103,10 +19237,14 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q243" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q243" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
@@ -19172,9 +19310,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N244" s="6" t="n">
-        <v>48.119</v>
-      </c>
+      <c r="N244" s="4" t="n"/>
       <c r="O244" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19182,10 +19318,14 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q244" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q244" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
@@ -19251,9 +19391,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N245" s="6" t="n">
-        <v>47.914</v>
-      </c>
+      <c r="N245" s="4" t="n"/>
       <c r="O245" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19261,10 +19399,14 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q245" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q245" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
@@ -19330,9 +19472,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N246" s="6" t="n">
-        <v>48.527</v>
-      </c>
+      <c r="N246" s="4" t="n"/>
       <c r="O246" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19340,10 +19480,14 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q246" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q246" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
@@ -19409,9 +19553,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N247" s="6" t="n">
-        <v>47.765</v>
-      </c>
+      <c r="N247" s="4" t="n"/>
       <c r="O247" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19419,10 +19561,14 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q247" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q247" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
@@ -19488,9 +19634,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N248" s="6" t="n">
-        <v>46.462</v>
-      </c>
+      <c r="N248" s="4" t="n"/>
       <c r="O248" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19498,10 +19642,14 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q248" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q248" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
@@ -19567,9 +19715,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N249" s="6" t="n">
-        <v>47.558</v>
-      </c>
+      <c r="N249" s="4" t="n"/>
       <c r="O249" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19577,10 +19723,14 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q249" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q249" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
@@ -19646,9 +19796,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N250" s="6" t="n">
-        <v>49.457</v>
-      </c>
+      <c r="N250" s="4" t="n"/>
       <c r="O250" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19656,10 +19804,14 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q250" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q250" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
@@ -19725,9 +19877,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N251" s="6" t="n">
-        <v>50.019</v>
-      </c>
+      <c r="N251" s="4" t="n"/>
       <c r="O251" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19735,10 +19885,14 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q251" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q251" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
@@ -19804,9 +19958,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N252" s="6" t="n">
-        <v>49.726</v>
-      </c>
+      <c r="N252" s="4" t="n"/>
       <c r="O252" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19814,10 +19966,14 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q252" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q252" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
@@ -19883,9 +20039,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N253" s="6" t="n">
-        <v>49.734</v>
-      </c>
+      <c r="N253" s="4" t="n"/>
       <c r="O253" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19893,10 +20047,14 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q253" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q253" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
@@ -19962,9 +20120,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N254" s="6" t="n">
-        <v>50.004</v>
-      </c>
+      <c r="N254" s="4" t="n"/>
       <c r="O254" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19972,10 +20128,14 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q254" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q254" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
@@ -20041,9 +20201,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N255" s="6" t="n">
-        <v>49.601</v>
-      </c>
+      <c r="N255" s="4" t="n"/>
       <c r="O255" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20051,10 +20209,14 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q255" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q255" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
@@ -20120,9 +20282,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N256" s="6" t="n">
-        <v>49.643</v>
-      </c>
+      <c r="N256" s="4" t="n"/>
       <c r="O256" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20130,10 +20290,14 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q256" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q256" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
@@ -20199,9 +20363,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N257" s="6" t="n">
-        <v>49.493</v>
-      </c>
+      <c r="N257" s="4" t="n"/>
       <c r="O257" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20209,10 +20371,14 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q257" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q257" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
@@ -20278,9 +20444,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N258" s="6" t="n">
-        <v>49.084</v>
-      </c>
+      <c r="N258" s="4" t="n"/>
       <c r="O258" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20288,10 +20452,14 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q258" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q258" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
@@ -20357,9 +20525,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N259" s="6" t="n">
-        <v>48.676</v>
-      </c>
+      <c r="N259" s="4" t="n"/>
       <c r="O259" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20367,10 +20533,14 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q259" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q259" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
@@ -20436,9 +20606,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N260" s="6" t="n">
-        <v>48.27</v>
-      </c>
+      <c r="N260" s="4" t="n"/>
       <c r="O260" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20446,10 +20614,14 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q260" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q260" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
@@ -20515,9 +20687,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N261" s="6" t="n">
-        <v>47.867</v>
-      </c>
+      <c r="N261" s="4" t="n"/>
       <c r="O261" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20525,10 +20695,14 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q261" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q261" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
@@ -20594,9 +20768,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N262" s="6" t="n">
-        <v>46.185</v>
-      </c>
+      <c r="N262" s="4" t="n"/>
       <c r="O262" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20604,10 +20776,14 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q262" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q262" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
@@ -20673,9 +20849,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N263" s="6" t="n">
-        <v>44.85</v>
-      </c>
+      <c r="N263" s="4" t="n"/>
       <c r="O263" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20683,10 +20857,14 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q263" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q263" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
@@ -20752,9 +20930,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N264" s="6" t="n">
-        <v>42.344</v>
-      </c>
+      <c r="N264" s="4" t="n"/>
       <c r="O264" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20762,10 +20938,14 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q264" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q264" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
@@ -20831,9 +21011,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N265" s="6" t="n">
-        <v>36.887</v>
-      </c>
+      <c r="N265" s="4" t="n"/>
       <c r="O265" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20841,10 +21019,14 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q265" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q265" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
@@ -20910,9 +21092,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N266" s="6" t="n">
-        <v>37.368</v>
-      </c>
+      <c r="N266" s="4" t="n"/>
       <c r="O266" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20920,10 +21100,14 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q266" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q266" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
@@ -20989,9 +21173,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N267" s="6" t="n">
-        <v>35.32</v>
-      </c>
+      <c r="N267" s="4" t="n"/>
       <c r="O267" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20999,10 +21181,14 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q267" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q267" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
@@ -21068,9 +21254,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N268" s="6" t="n">
-        <v>36.158</v>
-      </c>
+      <c r="N268" s="4" t="n"/>
       <c r="O268" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21078,10 +21262,14 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q268" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q268" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
@@ -21147,9 +21335,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N269" s="6" t="n">
-        <v>37.332</v>
-      </c>
+      <c r="N269" s="4" t="n"/>
       <c r="O269" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21157,10 +21343,14 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q269" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q269" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
@@ -21226,9 +21416,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N270" s="6" t="n">
-        <v>37.098</v>
-      </c>
+      <c r="N270" s="4" t="n"/>
       <c r="O270" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21236,10 +21424,14 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q270" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q270" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
@@ -21273,7 +21465,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21297,12 +21489,12 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>SL.UEM.TOTL.FE.ZS</t>
+          <t>SL.TLF.CACT.FE.ZS</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Desempleo femenino</t>
+          <t>Participación laboral femenina</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21313,10 +21505,14 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -21350,7 +21546,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21390,7 +21586,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21427,7 +21623,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21467,7 +21663,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21504,7 +21700,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21544,7 +21740,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21581,7 +21777,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21621,7 +21817,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21658,7 +21854,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21698,7 +21894,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21735,7 +21931,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21775,7 +21971,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21812,7 +22008,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -21852,7 +22048,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21889,7 +22085,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -21929,7 +22125,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21966,7 +22162,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22006,7 +22202,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22043,7 +22239,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22083,7 +22279,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22120,7 +22316,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22160,7 +22356,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22197,7 +22393,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22237,7 +22433,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22274,7 +22470,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22314,7 +22510,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22351,7 +22547,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22391,7 +22587,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22428,7 +22624,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22468,7 +22664,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22505,7 +22701,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22545,7 +22741,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22582,7 +22778,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22622,7 +22818,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22659,7 +22855,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22699,7 +22895,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22736,7 +22932,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22776,7 +22972,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22813,7 +23009,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -22853,7 +23049,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22890,7 +23086,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -22930,7 +23126,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22967,7 +23163,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23007,7 +23203,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23044,7 +23240,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23084,7 +23280,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23121,7 +23317,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23161,7 +23357,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23198,7 +23394,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23238,7 +23434,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23275,7 +23471,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23315,7 +23511,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23352,7 +23548,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23392,7 +23588,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23429,7 +23625,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23469,7 +23665,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23506,7 +23702,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23546,7 +23742,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23583,7 +23779,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23623,7 +23819,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23660,7 +23856,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23692,9 +23888,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N302" s="6" t="n">
-        <v>9.32</v>
-      </c>
+      <c r="N302" s="4" t="n"/>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23702,7 +23896,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23739,7 +23933,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23772,7 +23966,7 @@
         </is>
       </c>
       <c r="N303" s="6" t="n">
-        <v>6.925</v>
+        <v>9.32</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -23781,7 +23975,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23818,7 +24012,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -23851,7 +24045,7 @@
         </is>
       </c>
       <c r="N304" s="6" t="n">
-        <v>5.679</v>
+        <v>6.925</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -23860,7 +24054,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23897,7 +24091,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -23930,7 +24124,7 @@
         </is>
       </c>
       <c r="N305" s="6" t="n">
-        <v>9.557</v>
+        <v>5.679</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -23939,7 +24133,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23976,7 +24170,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24009,7 +24203,7 @@
         </is>
       </c>
       <c r="N306" s="6" t="n">
-        <v>12.604</v>
+        <v>9.557</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24018,7 +24212,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24055,7 +24249,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24088,7 +24282,7 @@
         </is>
       </c>
       <c r="N307" s="6" t="n">
-        <v>14.345</v>
+        <v>12.604</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24097,7 +24291,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24134,7 +24328,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24167,7 +24361,7 @@
         </is>
       </c>
       <c r="N308" s="6" t="n">
-        <v>13.627</v>
+        <v>14.345</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24176,7 +24370,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24213,7 +24407,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24246,7 +24440,7 @@
         </is>
       </c>
       <c r="N309" s="6" t="n">
-        <v>13.306</v>
+        <v>13.627</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24255,7 +24449,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24292,7 +24486,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24325,7 +24519,7 @@
         </is>
       </c>
       <c r="N310" s="6" t="n">
-        <v>16.482</v>
+        <v>13.306</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24334,7 +24528,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24371,7 +24565,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24404,7 +24598,7 @@
         </is>
       </c>
       <c r="N311" s="6" t="n">
-        <v>14.605</v>
+        <v>16.482</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24413,7 +24607,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24450,7 +24644,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24483,7 +24677,7 @@
         </is>
       </c>
       <c r="N312" s="6" t="n">
-        <v>14.109</v>
+        <v>14.605</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24492,7 +24686,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24529,7 +24723,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24562,7 +24756,7 @@
         </is>
       </c>
       <c r="N313" s="6" t="n">
-        <v>18.895</v>
+        <v>14.109</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24571,7 +24765,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24608,7 +24802,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24641,7 +24835,7 @@
         </is>
       </c>
       <c r="N314" s="6" t="n">
-        <v>20.483</v>
+        <v>18.895</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24650,7 +24844,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24687,7 +24881,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24720,7 +24914,7 @@
         </is>
       </c>
       <c r="N315" s="6" t="n">
-        <v>17.974</v>
+        <v>20.483</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24729,7 +24923,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24766,7 +24960,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24799,7 +24993,7 @@
         </is>
       </c>
       <c r="N316" s="6" t="n">
-        <v>11.64</v>
+        <v>17.974</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -24808,7 +25002,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24845,7 +25039,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -24878,7 +25072,7 @@
         </is>
       </c>
       <c r="N317" s="6" t="n">
-        <v>9.380000000000001</v>
+        <v>11.64</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -24887,7 +25081,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24924,7 +25118,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -24957,7 +25151,7 @@
         </is>
       </c>
       <c r="N318" s="6" t="n">
-        <v>7.643</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -24966,7 +25160,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25003,7 +25197,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25036,7 +25230,7 @@
         </is>
       </c>
       <c r="N319" s="6" t="n">
-        <v>6.218</v>
+        <v>7.643</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25045,7 +25239,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25082,7 +25276,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25115,7 +25309,7 @@
         </is>
       </c>
       <c r="N320" s="6" t="n">
-        <v>5.965</v>
+        <v>6.218</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25124,7 +25318,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25161,7 +25355,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25194,7 +25388,7 @@
         </is>
       </c>
       <c r="N321" s="6" t="n">
-        <v>6.952</v>
+        <v>5.965</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25203,7 +25397,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25240,7 +25434,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25273,7 +25467,7 @@
         </is>
       </c>
       <c r="N322" s="6" t="n">
-        <v>7.206</v>
+        <v>6.952</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25282,7 +25476,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25319,7 +25513,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25352,7 +25546,7 @@
         </is>
       </c>
       <c r="N323" s="6" t="n">
-        <v>7.109</v>
+        <v>7.206</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25361,7 +25555,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25398,7 +25592,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25431,7 +25625,7 @@
         </is>
       </c>
       <c r="N324" s="6" t="n">
-        <v>8.605</v>
+        <v>7.109</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25440,7 +25634,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25477,7 +25671,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25510,7 +25704,7 @@
         </is>
       </c>
       <c r="N325" s="6" t="n">
-        <v>7.578</v>
+        <v>8.605</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25519,7 +25713,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25556,7 +25750,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25589,7 +25783,7 @@
         </is>
       </c>
       <c r="N326" s="6" t="n">
-        <v>6.572</v>
+        <v>7.578</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
@@ -25598,7 +25792,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25635,7 +25829,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25668,7 +25862,7 @@
         </is>
       </c>
       <c r="N327" s="6" t="n">
-        <v>5.413</v>
+        <v>6.572</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
@@ -25677,7 +25871,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25714,7 +25908,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25747,7 +25941,7 @@
         </is>
       </c>
       <c r="N328" s="6" t="n">
-        <v>5.858</v>
+        <v>5.413</v>
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
@@ -25756,7 +25950,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25793,7 +25987,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -25826,7 +26020,7 @@
         </is>
       </c>
       <c r="N329" s="6" t="n">
-        <v>6.178</v>
+        <v>5.858</v>
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
@@ -25835,7 +26029,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25872,7 +26066,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -25905,7 +26099,7 @@
         </is>
       </c>
       <c r="N330" s="6" t="n">
-        <v>6.497</v>
+        <v>6.178</v>
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
@@ -25914,7 +26108,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25951,7 +26145,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -25984,7 +26178,7 @@
         </is>
       </c>
       <c r="N331" s="6" t="n">
-        <v>7.907</v>
+        <v>6.497</v>
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
@@ -25993,7 +26187,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26030,7 +26224,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26063,7 +26257,7 @@
         </is>
       </c>
       <c r="N332" s="6" t="n">
-        <v>7.541</v>
+        <v>7.907</v>
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
@@ -26072,7 +26266,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26109,7 +26303,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26142,7 +26336,7 @@
         </is>
       </c>
       <c r="N333" s="6" t="n">
-        <v>6.179</v>
+        <v>7.541</v>
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
@@ -26151,7 +26345,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26188,7 +26382,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26221,7 +26415,7 @@
         </is>
       </c>
       <c r="N334" s="6" t="n">
-        <v>5.937</v>
+        <v>6.179</v>
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
@@ -26230,7 +26424,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26267,7 +26461,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26300,7 +26494,7 @@
         </is>
       </c>
       <c r="N335" s="6" t="n">
-        <v>5.845</v>
+        <v>5.937</v>
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
@@ -26309,7 +26503,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26346,52 +26540,131 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H336" s="4" t="inlineStr">
+        <is>
+          <t>Género</t>
+        </is>
+      </c>
+      <c r="I336" s="4" t="inlineStr">
+        <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="J336" s="4" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="K336" s="4" t="inlineStr">
+        <is>
+          <t>mercado_laboral</t>
+        </is>
+      </c>
+      <c r="L336" s="4" t="inlineStr">
+        <is>
+          <t>SL.UEM.TOTL.FE.ZS</t>
+        </is>
+      </c>
+      <c r="M336" s="4" t="inlineStr">
+        <is>
+          <t>Desempleo femenino</t>
+        </is>
+      </c>
+      <c r="N336" s="6" t="n">
+        <v>5.845</v>
+      </c>
+      <c r="O336" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P336" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q336" s="4" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="H336" s="4" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="I336" s="4" t="inlineStr">
-        <is>
-          <t>genero</t>
-        </is>
-      </c>
-      <c r="J336" s="4" t="inlineStr">
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>Género</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
         <is>
           <t>Mercado laboral</t>
         </is>
       </c>
-      <c r="K336" s="4" t="inlineStr">
+      <c r="K337" s="4" t="inlineStr">
         <is>
           <t>mercado_laboral</t>
         </is>
       </c>
-      <c r="L336" s="4" t="inlineStr">
+      <c r="L337" s="4" t="inlineStr">
         <is>
           <t>SL.UEM.TOTL.FE.ZS</t>
         </is>
       </c>
-      <c r="M336" s="4" t="inlineStr">
+      <c r="M337" s="4" t="inlineStr">
         <is>
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N336" s="6" t="n">
+      <c r="N337" s="6" t="n">
         <v>5.835</v>
       </c>
-      <c r="O336" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P336" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q336" s="4" t="n"/>
+      <c r="O337" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P337" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26473,7 +26746,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26767,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q337"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,14 +16159,10 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q205" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -16240,14 +16236,10 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q206" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -16321,14 +16313,10 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q207" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -16402,14 +16390,10 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q208" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -16483,14 +16467,10 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q209" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -16564,14 +16544,10 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q210" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q210" s="4" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -16645,14 +16621,10 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q211" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -16726,14 +16698,10 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q212" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -16807,14 +16775,10 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q213" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -16888,14 +16852,10 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q214" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -16969,14 +16929,10 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q215" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -17050,14 +17006,10 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q216" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -17131,14 +17083,10 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q217" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -17212,14 +17160,10 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q218" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q218" s="4" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -17293,14 +17237,10 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q219" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -17374,14 +17314,10 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q220" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -17455,14 +17391,10 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q221" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
@@ -17536,14 +17468,10 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q222" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -17617,14 +17545,10 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q223" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
@@ -17698,14 +17622,10 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q224" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q224" s="4" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -17779,14 +17699,10 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q225" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
@@ -17860,14 +17776,10 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q226" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
@@ -17941,14 +17853,10 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q227" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
@@ -18022,14 +17930,10 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q228" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
@@ -18103,14 +18007,10 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q229" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -18184,14 +18084,10 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q230" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
@@ -18265,14 +18161,10 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q231" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
@@ -18346,14 +18238,10 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q232" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q232" s="4" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
@@ -18427,14 +18315,10 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q233" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
@@ -18508,14 +18392,10 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q234" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -18581,7 +18461,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N235" s="4" t="n"/>
+      <c r="N235" s="6" t="n">
+        <v>48.56</v>
+      </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18589,14 +18471,10 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q235" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
@@ -18662,7 +18540,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N236" s="4" t="n"/>
+      <c r="N236" s="6" t="n">
+        <v>49.027</v>
+      </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18670,14 +18550,10 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q236" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
@@ -18743,7 +18619,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N237" s="4" t="n"/>
+      <c r="N237" s="6" t="n">
+        <v>49.439</v>
+      </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18751,14 +18629,10 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q237" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
@@ -18824,7 +18698,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N238" s="4" t="n"/>
+      <c r="N238" s="6" t="n">
+        <v>49.121</v>
+      </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18832,14 +18708,10 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q238" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q238" s="4" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -18905,7 +18777,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N239" s="4" t="n"/>
+      <c r="N239" s="6" t="n">
+        <v>48.519</v>
+      </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18913,14 +18787,10 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q239" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
@@ -18986,7 +18856,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n"/>
+      <c r="N240" s="6" t="n">
+        <v>48.502</v>
+      </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18994,14 +18866,10 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q240" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -19067,7 +18935,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N241" s="4" t="n"/>
+      <c r="N241" s="6" t="n">
+        <v>48.683</v>
+      </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19075,14 +18945,10 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q241" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
@@ -19148,7 +19014,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N242" s="4" t="n"/>
+      <c r="N242" s="6" t="n">
+        <v>48.743</v>
+      </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19156,14 +19024,10 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q242" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
@@ -19229,7 +19093,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N243" s="4" t="n"/>
+      <c r="N243" s="6" t="n">
+        <v>48.976</v>
+      </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19237,14 +19103,10 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q243" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
@@ -19310,7 +19172,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N244" s="4" t="n"/>
+      <c r="N244" s="6" t="n">
+        <v>48.119</v>
+      </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19318,14 +19182,10 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q244" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
@@ -19391,7 +19251,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N245" s="4" t="n"/>
+      <c r="N245" s="6" t="n">
+        <v>47.914</v>
+      </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19399,14 +19261,10 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q245" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
@@ -19472,7 +19330,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N246" s="4" t="n"/>
+      <c r="N246" s="6" t="n">
+        <v>48.527</v>
+      </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19480,14 +19340,10 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q246" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
@@ -19553,7 +19409,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N247" s="4" t="n"/>
+      <c r="N247" s="6" t="n">
+        <v>47.765</v>
+      </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19561,14 +19419,10 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q247" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
@@ -19634,7 +19488,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N248" s="4" t="n"/>
+      <c r="N248" s="6" t="n">
+        <v>46.462</v>
+      </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19642,14 +19498,10 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q248" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q248" s="4" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
@@ -19715,7 +19567,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N249" s="4" t="n"/>
+      <c r="N249" s="6" t="n">
+        <v>47.558</v>
+      </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19723,14 +19577,10 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q249" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
@@ -19796,7 +19646,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N250" s="4" t="n"/>
+      <c r="N250" s="6" t="n">
+        <v>49.457</v>
+      </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19804,14 +19656,10 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q250" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
@@ -19877,7 +19725,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N251" s="4" t="n"/>
+      <c r="N251" s="6" t="n">
+        <v>50.019</v>
+      </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19885,14 +19735,10 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q251" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
@@ -19958,7 +19804,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N252" s="4" t="n"/>
+      <c r="N252" s="6" t="n">
+        <v>49.726</v>
+      </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19966,14 +19814,10 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q252" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q252" s="4" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
@@ -20039,7 +19883,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N253" s="4" t="n"/>
+      <c r="N253" s="6" t="n">
+        <v>49.734</v>
+      </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20047,14 +19893,10 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q253" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
@@ -20120,7 +19962,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N254" s="4" t="n"/>
+      <c r="N254" s="6" t="n">
+        <v>50.004</v>
+      </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20128,14 +19972,10 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q254" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
@@ -20201,7 +20041,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N255" s="4" t="n"/>
+      <c r="N255" s="6" t="n">
+        <v>49.601</v>
+      </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20209,14 +20051,10 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q255" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
@@ -20282,7 +20120,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N256" s="4" t="n"/>
+      <c r="N256" s="6" t="n">
+        <v>49.643</v>
+      </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20290,14 +20130,10 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q256" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
@@ -20363,7 +20199,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N257" s="4" t="n"/>
+      <c r="N257" s="6" t="n">
+        <v>49.493</v>
+      </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20371,14 +20209,10 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q257" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
@@ -20444,7 +20278,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N258" s="4" t="n"/>
+      <c r="N258" s="6" t="n">
+        <v>49.084</v>
+      </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20452,14 +20288,10 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q258" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
@@ -20525,7 +20357,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N259" s="4" t="n"/>
+      <c r="N259" s="6" t="n">
+        <v>48.676</v>
+      </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20533,14 +20367,10 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q259" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
@@ -20606,7 +20436,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N260" s="4" t="n"/>
+      <c r="N260" s="6" t="n">
+        <v>48.27</v>
+      </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20614,14 +20446,10 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q260" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q260" s="4" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
@@ -20687,7 +20515,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N261" s="4" t="n"/>
+      <c r="N261" s="6" t="n">
+        <v>47.867</v>
+      </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20695,14 +20525,10 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q261" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
@@ -20768,7 +20594,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N262" s="4" t="n"/>
+      <c r="N262" s="6" t="n">
+        <v>46.185</v>
+      </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20776,14 +20604,10 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q262" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
@@ -20849,7 +20673,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N263" s="4" t="n"/>
+      <c r="N263" s="6" t="n">
+        <v>44.85</v>
+      </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20857,14 +20683,10 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q263" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
@@ -20930,7 +20752,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N264" s="4" t="n"/>
+      <c r="N264" s="6" t="n">
+        <v>42.344</v>
+      </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20938,14 +20762,10 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q264" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
@@ -21011,7 +20831,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N265" s="4" t="n"/>
+      <c r="N265" s="6" t="n">
+        <v>36.887</v>
+      </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21019,14 +20841,10 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q265" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
@@ -21092,7 +20910,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N266" s="4" t="n"/>
+      <c r="N266" s="6" t="n">
+        <v>37.368</v>
+      </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21100,14 +20920,10 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q266" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q266" s="4" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
@@ -21173,7 +20989,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N267" s="4" t="n"/>
+      <c r="N267" s="6" t="n">
+        <v>35.32</v>
+      </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21181,14 +20999,10 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q267" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
@@ -21254,7 +21068,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N268" s="4" t="n"/>
+      <c r="N268" s="6" t="n">
+        <v>36.158</v>
+      </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21262,14 +21078,10 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q268" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q268" s="4" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
@@ -21335,7 +21147,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N269" s="4" t="n"/>
+      <c r="N269" s="6" t="n">
+        <v>37.332</v>
+      </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21343,14 +21157,10 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q269" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
@@ -21416,7 +21226,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N270" s="4" t="n"/>
+      <c r="N270" s="6" t="n">
+        <v>37.098</v>
+      </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21424,14 +21236,10 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q270" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q270" s="4" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
@@ -21465,7 +21273,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>2026</v>
+        <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21489,12 +21297,12 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>SL.TLF.CACT.FE.ZS</t>
+          <t>SL.UEM.TOTL.FE.ZS</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Participación laboral femenina</t>
+          <t>Desempleo femenino</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21505,14 +21313,10 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -21546,7 +21350,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21586,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21623,7 +21427,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21663,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21700,7 +21504,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21740,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21777,7 +21581,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21817,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21854,7 +21658,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21894,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21931,7 +21735,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21971,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22008,7 +21812,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -22048,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22085,7 +21889,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -22125,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22162,7 +21966,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22202,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22239,7 +22043,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22279,7 +22083,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22316,7 +22120,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22356,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22393,7 +22197,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22433,7 +22237,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22470,7 +22274,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22510,7 +22314,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22547,7 +22351,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22587,7 +22391,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22624,7 +22428,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22664,7 +22468,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22701,7 +22505,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22741,7 +22545,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22778,7 +22582,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22818,7 +22622,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22855,7 +22659,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22895,7 +22699,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22932,7 +22736,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22972,7 +22776,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23009,7 +22813,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -23049,7 +22853,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23086,7 +22890,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -23126,7 +22930,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23163,7 +22967,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23203,7 +23007,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23240,7 +23044,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23280,7 +23084,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23317,7 +23121,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23357,7 +23161,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23394,7 +23198,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23434,7 +23238,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23471,7 +23275,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23511,7 +23315,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23548,7 +23352,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23588,7 +23392,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23625,7 +23429,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23665,7 +23469,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23702,7 +23506,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23742,7 +23546,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23779,7 +23583,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23819,7 +23623,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23856,7 +23660,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23888,7 +23692,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n"/>
+      <c r="N302" s="6" t="n">
+        <v>9.32</v>
+      </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23896,7 +23702,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23933,7 +23739,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23966,7 +23772,7 @@
         </is>
       </c>
       <c r="N303" s="6" t="n">
-        <v>9.32</v>
+        <v>6.925</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -23975,7 +23781,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24012,7 +23818,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -24045,7 +23851,7 @@
         </is>
       </c>
       <c r="N304" s="6" t="n">
-        <v>6.925</v>
+        <v>5.679</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -24054,7 +23860,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24091,7 +23897,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -24124,7 +23930,7 @@
         </is>
       </c>
       <c r="N305" s="6" t="n">
-        <v>5.679</v>
+        <v>9.557</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -24133,7 +23939,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24170,7 +23976,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24203,7 +24009,7 @@
         </is>
       </c>
       <c r="N306" s="6" t="n">
-        <v>9.557</v>
+        <v>12.604</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24212,7 +24018,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24249,7 +24055,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24282,7 +24088,7 @@
         </is>
       </c>
       <c r="N307" s="6" t="n">
-        <v>12.604</v>
+        <v>14.345</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24291,7 +24097,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24328,7 +24134,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24361,7 +24167,7 @@
         </is>
       </c>
       <c r="N308" s="6" t="n">
-        <v>14.345</v>
+        <v>13.627</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24370,7 +24176,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24407,7 +24213,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24440,7 +24246,7 @@
         </is>
       </c>
       <c r="N309" s="6" t="n">
-        <v>13.627</v>
+        <v>13.306</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24449,7 +24255,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24486,7 +24292,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24519,7 +24325,7 @@
         </is>
       </c>
       <c r="N310" s="6" t="n">
-        <v>13.306</v>
+        <v>16.482</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24528,7 +24334,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24565,7 +24371,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24598,7 +24404,7 @@
         </is>
       </c>
       <c r="N311" s="6" t="n">
-        <v>16.482</v>
+        <v>14.605</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24607,7 +24413,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24644,7 +24450,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24677,7 +24483,7 @@
         </is>
       </c>
       <c r="N312" s="6" t="n">
-        <v>14.605</v>
+        <v>14.109</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24686,7 +24492,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24723,7 +24529,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24756,7 +24562,7 @@
         </is>
       </c>
       <c r="N313" s="6" t="n">
-        <v>14.109</v>
+        <v>18.895</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24765,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24802,7 +24608,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24835,7 +24641,7 @@
         </is>
       </c>
       <c r="N314" s="6" t="n">
-        <v>18.895</v>
+        <v>20.483</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24844,7 +24650,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24881,7 +24687,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24914,7 +24720,7 @@
         </is>
       </c>
       <c r="N315" s="6" t="n">
-        <v>20.483</v>
+        <v>17.974</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24923,7 +24729,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24960,7 +24766,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24993,7 +24799,7 @@
         </is>
       </c>
       <c r="N316" s="6" t="n">
-        <v>17.974</v>
+        <v>11.64</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -25002,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25039,7 +24845,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -25072,7 +24878,7 @@
         </is>
       </c>
       <c r="N317" s="6" t="n">
-        <v>11.64</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -25081,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25118,7 +24924,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -25151,7 +24957,7 @@
         </is>
       </c>
       <c r="N318" s="6" t="n">
-        <v>9.380000000000001</v>
+        <v>7.643</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -25160,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25197,7 +25003,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25230,7 +25036,7 @@
         </is>
       </c>
       <c r="N319" s="6" t="n">
-        <v>7.643</v>
+        <v>6.218</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25239,7 +25045,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25276,7 +25082,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25309,7 +25115,7 @@
         </is>
       </c>
       <c r="N320" s="6" t="n">
-        <v>6.218</v>
+        <v>5.965</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25318,7 +25124,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25355,7 +25161,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25388,7 +25194,7 @@
         </is>
       </c>
       <c r="N321" s="6" t="n">
-        <v>5.965</v>
+        <v>6.952</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25397,7 +25203,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25434,7 +25240,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25467,7 +25273,7 @@
         </is>
       </c>
       <c r="N322" s="6" t="n">
-        <v>6.952</v>
+        <v>7.206</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25476,7 +25282,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25513,7 +25319,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25546,7 +25352,7 @@
         </is>
       </c>
       <c r="N323" s="6" t="n">
-        <v>7.206</v>
+        <v>7.109</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25555,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25592,7 +25398,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25625,7 +25431,7 @@
         </is>
       </c>
       <c r="N324" s="6" t="n">
-        <v>7.109</v>
+        <v>8.605</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25634,7 +25440,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25671,7 +25477,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25704,7 +25510,7 @@
         </is>
       </c>
       <c r="N325" s="6" t="n">
-        <v>8.605</v>
+        <v>7.578</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25713,7 +25519,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25750,7 +25556,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25783,7 +25589,7 @@
         </is>
       </c>
       <c r="N326" s="6" t="n">
-        <v>7.578</v>
+        <v>6.572</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
@@ -25792,7 +25598,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25829,7 +25635,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25862,7 +25668,7 @@
         </is>
       </c>
       <c r="N327" s="6" t="n">
-        <v>6.572</v>
+        <v>5.413</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
@@ -25871,7 +25677,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25908,7 +25714,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25941,7 +25747,7 @@
         </is>
       </c>
       <c r="N328" s="6" t="n">
-        <v>5.413</v>
+        <v>5.858</v>
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
@@ -25950,7 +25756,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25987,7 +25793,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -26020,7 +25826,7 @@
         </is>
       </c>
       <c r="N329" s="6" t="n">
-        <v>5.858</v>
+        <v>6.178</v>
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
@@ -26029,7 +25835,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26066,7 +25872,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -26099,7 +25905,7 @@
         </is>
       </c>
       <c r="N330" s="6" t="n">
-        <v>6.178</v>
+        <v>6.497</v>
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
@@ -26108,7 +25914,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26145,7 +25951,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26178,7 +25984,7 @@
         </is>
       </c>
       <c r="N331" s="6" t="n">
-        <v>6.497</v>
+        <v>7.907</v>
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
@@ -26187,7 +25993,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26224,7 +26030,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26257,7 +26063,7 @@
         </is>
       </c>
       <c r="N332" s="6" t="n">
-        <v>7.907</v>
+        <v>7.541</v>
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
@@ -26266,7 +26072,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26303,7 +26109,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26336,7 +26142,7 @@
         </is>
       </c>
       <c r="N333" s="6" t="n">
-        <v>7.541</v>
+        <v>6.179</v>
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
@@ -26345,7 +26151,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26382,7 +26188,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26415,7 +26221,7 @@
         </is>
       </c>
       <c r="N334" s="6" t="n">
-        <v>6.179</v>
+        <v>5.937</v>
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
@@ -26424,7 +26230,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26461,7 +26267,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26494,7 +26300,7 @@
         </is>
       </c>
       <c r="N335" s="6" t="n">
-        <v>5.937</v>
+        <v>5.845</v>
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
@@ -26503,7 +26309,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26540,7 +26346,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26573,7 +26379,7 @@
         </is>
       </c>
       <c r="N336" s="6" t="n">
-        <v>5.845</v>
+        <v>5.835</v>
       </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
@@ -26582,89 +26388,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>genero</t>
-        </is>
-      </c>
-      <c r="J337" s="4" t="inlineStr">
-        <is>
-          <t>Mercado laboral</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>mercado_laboral</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>SL.UEM.TOTL.FE.ZS</t>
-        </is>
-      </c>
-      <c r="M337" s="4" t="inlineStr">
-        <is>
-          <t>Desempleo femenino</t>
-        </is>
-      </c>
-      <c r="N337" s="6" t="n">
-        <v>5.835</v>
-      </c>
-      <c r="O337" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P337" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26746,7 +26473,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26494,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q336"/>
+  <dimension ref="A1:Q337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21313,10 +21313,14 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -21390,10 +21394,14 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q272" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q272" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -21467,10 +21475,14 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q273" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q273" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -21544,10 +21556,14 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q274" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q274" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -21621,10 +21637,14 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q275" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q275" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -21698,10 +21718,14 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q276" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q276" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -21775,10 +21799,14 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q277" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q277" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -21852,10 +21880,14 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q278" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q278" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -21929,10 +21961,14 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q279" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q279" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -22006,10 +22042,14 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q280" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q280" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -22083,10 +22123,14 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q281" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q281" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
@@ -22160,10 +22204,14 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q282" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q282" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -22237,10 +22285,14 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q283" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q283" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
@@ -22314,10 +22366,14 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q284" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q284" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -22391,10 +22447,14 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q285" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q285" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
@@ -22468,10 +22528,14 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q286" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q286" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -22545,10 +22609,14 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q287" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q287" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
@@ -22622,10 +22690,14 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q288" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q288" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -22699,10 +22771,14 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q289" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q289" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
@@ -22776,10 +22852,14 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q290" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q290" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -22853,10 +22933,14 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q291" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q291" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -22930,10 +23014,14 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q292" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q292" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -23007,10 +23095,14 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q293" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q293" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
@@ -23084,10 +23176,14 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q294" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q294" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -23161,10 +23257,14 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q295" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q295" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
@@ -23238,10 +23338,14 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q296" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q296" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -23315,10 +23419,14 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q297" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q297" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
@@ -23392,10 +23500,14 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q298" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q298" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -23469,10 +23581,14 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q299" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q299" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
@@ -23546,10 +23662,14 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q300" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q300" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -23623,10 +23743,14 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q301" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q301" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
@@ -23692,9 +23816,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N302" s="6" t="n">
-        <v>9.32</v>
-      </c>
+      <c r="N302" s="4" t="n"/>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23702,10 +23824,14 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q302" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q302" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -23771,9 +23897,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N303" s="6" t="n">
-        <v>6.925</v>
-      </c>
+      <c r="N303" s="4" t="n"/>
       <c r="O303" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23781,10 +23905,14 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q303" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q303" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
@@ -23850,9 +23978,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N304" s="6" t="n">
-        <v>5.679</v>
-      </c>
+      <c r="N304" s="4" t="n"/>
       <c r="O304" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23860,10 +23986,14 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q304" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q304" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -23929,9 +24059,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N305" s="6" t="n">
-        <v>9.557</v>
-      </c>
+      <c r="N305" s="4" t="n"/>
       <c r="O305" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23939,10 +24067,14 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q305" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q305" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -24008,9 +24140,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N306" s="6" t="n">
-        <v>12.604</v>
-      </c>
+      <c r="N306" s="4" t="n"/>
       <c r="O306" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24018,10 +24148,14 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q306" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q306" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -24087,9 +24221,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N307" s="6" t="n">
-        <v>14.345</v>
-      </c>
+      <c r="N307" s="4" t="n"/>
       <c r="O307" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24097,10 +24229,14 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q307" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q307" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -24166,9 +24302,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N308" s="6" t="n">
-        <v>13.627</v>
-      </c>
+      <c r="N308" s="4" t="n"/>
       <c r="O308" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24176,10 +24310,14 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q308" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q308" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -24245,9 +24383,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N309" s="6" t="n">
-        <v>13.306</v>
-      </c>
+      <c r="N309" s="4" t="n"/>
       <c r="O309" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24255,10 +24391,14 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q309" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q309" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
@@ -24324,9 +24464,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N310" s="6" t="n">
-        <v>16.482</v>
-      </c>
+      <c r="N310" s="4" t="n"/>
       <c r="O310" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24334,10 +24472,14 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q310" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q310" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -24403,9 +24545,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N311" s="6" t="n">
-        <v>14.605</v>
-      </c>
+      <c r="N311" s="4" t="n"/>
       <c r="O311" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24413,10 +24553,14 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q311" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q311" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
@@ -24482,9 +24626,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N312" s="6" t="n">
-        <v>14.109</v>
-      </c>
+      <c r="N312" s="4" t="n"/>
       <c r="O312" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24492,10 +24634,14 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q312" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q312" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -24561,9 +24707,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N313" s="6" t="n">
-        <v>18.895</v>
-      </c>
+      <c r="N313" s="4" t="n"/>
       <c r="O313" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24571,10 +24715,14 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q313" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q313" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
@@ -24640,9 +24788,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N314" s="6" t="n">
-        <v>20.483</v>
-      </c>
+      <c r="N314" s="4" t="n"/>
       <c r="O314" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24650,10 +24796,14 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q314" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q314" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -24719,9 +24869,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N315" s="6" t="n">
-        <v>17.974</v>
-      </c>
+      <c r="N315" s="4" t="n"/>
       <c r="O315" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24729,10 +24877,14 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q315" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q315" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
@@ -24798,9 +24950,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N316" s="6" t="n">
-        <v>11.64</v>
-      </c>
+      <c r="N316" s="4" t="n"/>
       <c r="O316" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24808,10 +24958,14 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q316" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q316" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -24877,9 +25031,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N317" s="6" t="n">
-        <v>9.380000000000001</v>
-      </c>
+      <c r="N317" s="4" t="n"/>
       <c r="O317" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24887,10 +25039,14 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q317" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q317" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
@@ -24956,9 +25112,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N318" s="6" t="n">
-        <v>7.643</v>
-      </c>
+      <c r="N318" s="4" t="n"/>
       <c r="O318" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24966,10 +25120,14 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q318" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q318" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -25035,9 +25193,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N319" s="6" t="n">
-        <v>6.218</v>
-      </c>
+      <c r="N319" s="4" t="n"/>
       <c r="O319" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25045,10 +25201,14 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q319" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q319" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -25114,9 +25274,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N320" s="6" t="n">
-        <v>5.965</v>
-      </c>
+      <c r="N320" s="4" t="n"/>
       <c r="O320" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25124,10 +25282,14 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q320" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q320" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -25193,9 +25355,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N321" s="6" t="n">
-        <v>6.952</v>
-      </c>
+      <c r="N321" s="4" t="n"/>
       <c r="O321" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25203,10 +25363,14 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q321" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q321" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -25272,9 +25436,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N322" s="6" t="n">
-        <v>7.206</v>
-      </c>
+      <c r="N322" s="4" t="n"/>
       <c r="O322" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25282,10 +25444,14 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q322" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q322" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -25351,9 +25517,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N323" s="6" t="n">
-        <v>7.109</v>
-      </c>
+      <c r="N323" s="4" t="n"/>
       <c r="O323" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25361,10 +25525,14 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q323" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q323" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
@@ -25430,9 +25598,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N324" s="6" t="n">
-        <v>8.605</v>
-      </c>
+      <c r="N324" s="4" t="n"/>
       <c r="O324" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25440,10 +25606,14 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q324" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q324" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -25509,9 +25679,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N325" s="6" t="n">
-        <v>7.578</v>
-      </c>
+      <c r="N325" s="4" t="n"/>
       <c r="O325" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25519,10 +25687,14 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q325" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q325" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
@@ -25588,9 +25760,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N326" s="6" t="n">
-        <v>6.572</v>
-      </c>
+      <c r="N326" s="4" t="n"/>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25598,10 +25768,14 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q326" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q326" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -25667,9 +25841,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N327" s="6" t="n">
-        <v>5.413</v>
-      </c>
+      <c r="N327" s="4" t="n"/>
       <c r="O327" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25677,10 +25849,14 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q327" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q327" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
@@ -25746,9 +25922,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N328" s="6" t="n">
-        <v>5.858</v>
-      </c>
+      <c r="N328" s="4" t="n"/>
       <c r="O328" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25756,10 +25930,14 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q328" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q328" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -25825,9 +26003,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N329" s="6" t="n">
-        <v>6.178</v>
-      </c>
+      <c r="N329" s="4" t="n"/>
       <c r="O329" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25835,10 +26011,14 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q329" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q329" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
@@ -25904,9 +26084,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N330" s="6" t="n">
-        <v>6.497</v>
-      </c>
+      <c r="N330" s="4" t="n"/>
       <c r="O330" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25914,10 +26092,14 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q330" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q330" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -25983,9 +26165,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N331" s="6" t="n">
-        <v>7.907</v>
-      </c>
+      <c r="N331" s="4" t="n"/>
       <c r="O331" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25993,10 +26173,14 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q331" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q331" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
@@ -26062,9 +26246,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N332" s="6" t="n">
-        <v>7.541</v>
-      </c>
+      <c r="N332" s="4" t="n"/>
       <c r="O332" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26072,10 +26254,14 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q332" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q332" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -26141,9 +26327,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N333" s="6" t="n">
-        <v>6.179</v>
-      </c>
+      <c r="N333" s="4" t="n"/>
       <c r="O333" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26151,10 +26335,14 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q333" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q333" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
@@ -26220,9 +26408,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N334" s="6" t="n">
-        <v>5.937</v>
-      </c>
+      <c r="N334" s="4" t="n"/>
       <c r="O334" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26230,10 +26416,14 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q334" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q334" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -26299,9 +26489,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N335" s="6" t="n">
-        <v>5.845</v>
-      </c>
+      <c r="N335" s="4" t="n"/>
       <c r="O335" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26309,10 +26497,14 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q335" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q335" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
@@ -26378,9 +26570,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N336" s="6" t="n">
-        <v>5.835</v>
-      </c>
+      <c r="N336" s="4" t="n"/>
       <c r="O336" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26388,10 +26578,95 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Q336" s="4" t="n"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q336" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>Género</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>mercado_laboral</t>
+        </is>
+      </c>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>SL.UEM.TOTL.FE.ZS</t>
+        </is>
+      </c>
+      <c r="M337" s="4" t="inlineStr">
+        <is>
+          <t>Desempleo femenino</t>
+        </is>
+      </c>
+      <c r="N337" s="4" t="n"/>
+      <c r="O337" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P337" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q337" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26473,7 +26748,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26769,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q337"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21313,14 +21313,10 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -21394,14 +21390,10 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q272" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q272" s="4" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -21475,14 +21467,10 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q273" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -21556,14 +21544,10 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q274" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q274" s="4" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -21637,14 +21621,10 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q275" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -21718,14 +21698,10 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q276" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q276" s="4" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -21799,14 +21775,10 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q277" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -21880,14 +21852,10 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q278" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -21961,14 +21929,10 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q279" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -22042,14 +22006,10 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q280" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q280" s="4" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -22123,14 +22083,10 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q281" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
@@ -22204,14 +22160,10 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q282" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -22285,14 +22237,10 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q283" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
@@ -22366,14 +22314,10 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q284" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -22447,14 +22391,10 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q285" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
@@ -22528,14 +22468,10 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q286" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -22609,14 +22545,10 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q287" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
@@ -22690,14 +22622,10 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q288" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q288" s="4" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -22771,14 +22699,10 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q289" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
@@ -22852,14 +22776,10 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q290" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -22933,14 +22853,10 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q291" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -23014,14 +22930,10 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q292" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -23095,14 +23007,10 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q293" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
@@ -23176,14 +23084,10 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q294" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q294" s="4" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -23257,14 +23161,10 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q295" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
@@ -23338,14 +23238,10 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q296" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -23419,14 +23315,10 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q297" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
@@ -23500,14 +23392,10 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q298" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -23581,14 +23469,10 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q299" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
@@ -23662,14 +23546,10 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q300" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -23743,14 +23623,10 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q301" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
@@ -23816,7 +23692,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n"/>
+      <c r="N302" s="6" t="n">
+        <v>9.32</v>
+      </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23824,14 +23702,10 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q302" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q302" s="4" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -23897,7 +23771,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n"/>
+      <c r="N303" s="6" t="n">
+        <v>6.925</v>
+      </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23905,14 +23781,10 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q303" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
@@ -23978,7 +23850,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n"/>
+      <c r="N304" s="6" t="n">
+        <v>5.679</v>
+      </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23986,14 +23860,10 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q304" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -24059,7 +23929,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n"/>
+      <c r="N305" s="6" t="n">
+        <v>9.557</v>
+      </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24067,14 +23939,10 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q305" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -24140,7 +24008,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n"/>
+      <c r="N306" s="6" t="n">
+        <v>12.604</v>
+      </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24148,14 +24018,10 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q306" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -24221,7 +24087,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n"/>
+      <c r="N307" s="6" t="n">
+        <v>14.345</v>
+      </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24229,14 +24097,10 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q307" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -24302,7 +24166,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n"/>
+      <c r="N308" s="6" t="n">
+        <v>13.627</v>
+      </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24310,14 +24176,10 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q308" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q308" s="4" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -24383,7 +24245,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n"/>
+      <c r="N309" s="6" t="n">
+        <v>13.306</v>
+      </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24391,14 +24255,10 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q309" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
@@ -24464,7 +24324,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n"/>
+      <c r="N310" s="6" t="n">
+        <v>16.482</v>
+      </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24472,14 +24334,10 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q310" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q310" s="4" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -24545,7 +24403,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n"/>
+      <c r="N311" s="6" t="n">
+        <v>14.605</v>
+      </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24553,14 +24413,10 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q311" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
@@ -24626,7 +24482,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n"/>
+      <c r="N312" s="6" t="n">
+        <v>14.109</v>
+      </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24634,14 +24492,10 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q312" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q312" s="4" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -24707,7 +24561,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n"/>
+      <c r="N313" s="6" t="n">
+        <v>18.895</v>
+      </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24715,14 +24571,10 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q313" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
@@ -24788,7 +24640,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n"/>
+      <c r="N314" s="6" t="n">
+        <v>20.483</v>
+      </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24796,14 +24650,10 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q314" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q314" s="4" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -24869,7 +24719,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n"/>
+      <c r="N315" s="6" t="n">
+        <v>17.974</v>
+      </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24877,14 +24729,10 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q315" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
@@ -24950,7 +24798,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n"/>
+      <c r="N316" s="6" t="n">
+        <v>11.64</v>
+      </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24958,14 +24808,10 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q316" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q316" s="4" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -25031,7 +24877,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n"/>
+      <c r="N317" s="6" t="n">
+        <v>9.380000000000001</v>
+      </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25039,14 +24887,10 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q317" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
@@ -25112,7 +24956,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n"/>
+      <c r="N318" s="6" t="n">
+        <v>7.643</v>
+      </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25120,14 +24966,10 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q318" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q318" s="4" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -25193,7 +25035,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n"/>
+      <c r="N319" s="6" t="n">
+        <v>6.218</v>
+      </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25201,14 +25045,10 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q319" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -25274,7 +25114,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n"/>
+      <c r="N320" s="6" t="n">
+        <v>5.965</v>
+      </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25282,14 +25124,10 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q320" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q320" s="4" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -25355,7 +25193,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n"/>
+      <c r="N321" s="6" t="n">
+        <v>6.952</v>
+      </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25363,14 +25203,10 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q321" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -25436,7 +25272,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n"/>
+      <c r="N322" s="6" t="n">
+        <v>7.206</v>
+      </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25444,14 +25282,10 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q322" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q322" s="4" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -25517,7 +25351,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n"/>
+      <c r="N323" s="6" t="n">
+        <v>7.109</v>
+      </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25525,14 +25361,10 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q323" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
@@ -25598,7 +25430,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n"/>
+      <c r="N324" s="6" t="n">
+        <v>8.605</v>
+      </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25606,14 +25440,10 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q324" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -25679,7 +25509,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n"/>
+      <c r="N325" s="6" t="n">
+        <v>7.578</v>
+      </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25687,14 +25519,10 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q325" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
@@ -25760,7 +25588,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="6" t="n">
+        <v>6.572</v>
+      </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25768,14 +25598,10 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q326" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -25841,7 +25667,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N327" s="4" t="n"/>
+      <c r="N327" s="6" t="n">
+        <v>5.413</v>
+      </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25849,14 +25677,10 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q327" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
@@ -25922,7 +25746,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N328" s="4" t="n"/>
+      <c r="N328" s="6" t="n">
+        <v>5.858</v>
+      </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25930,14 +25756,10 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q328" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q328" s="4" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -26003,7 +25825,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N329" s="4" t="n"/>
+      <c r="N329" s="6" t="n">
+        <v>6.178</v>
+      </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26011,14 +25835,10 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q329" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
@@ -26084,7 +25904,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N330" s="4" t="n"/>
+      <c r="N330" s="6" t="n">
+        <v>6.497</v>
+      </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26092,14 +25914,10 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q330" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q330" s="4" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -26165,7 +25983,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N331" s="4" t="n"/>
+      <c r="N331" s="6" t="n">
+        <v>7.907</v>
+      </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26173,14 +25993,10 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q331" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
@@ -26246,7 +26062,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N332" s="4" t="n"/>
+      <c r="N332" s="6" t="n">
+        <v>7.541</v>
+      </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26254,14 +26072,10 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q332" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -26327,7 +26141,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N333" s="4" t="n"/>
+      <c r="N333" s="6" t="n">
+        <v>6.179</v>
+      </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26335,14 +26151,10 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q333" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
@@ -26408,7 +26220,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N334" s="4" t="n"/>
+      <c r="N334" s="6" t="n">
+        <v>5.937</v>
+      </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26416,14 +26230,10 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q334" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q334" s="4" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -26489,7 +26299,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N335" s="4" t="n"/>
+      <c r="N335" s="6" t="n">
+        <v>5.845</v>
+      </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26497,14 +26309,10 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q335" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
@@ -26570,7 +26378,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N336" s="4" t="n"/>
+      <c r="N336" s="6" t="n">
+        <v>5.835</v>
+      </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26578,95 +26388,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q336" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>genero</t>
-        </is>
-      </c>
-      <c r="J337" s="4" t="inlineStr">
-        <is>
-          <t>Mercado laboral</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>mercado_laboral</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>SL.UEM.TOTL.FE.ZS</t>
-        </is>
-      </c>
-      <c r="M337" s="4" t="inlineStr">
-        <is>
-          <t>Desempleo femenino</t>
-        </is>
-      </c>
-      <c r="N337" s="4" t="n"/>
-      <c r="O337" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P337" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q336" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26748,7 +26473,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26494,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
